--- a/wr_sdm/consequence_tables/weights.xlsx
+++ b/wr_sdm/consequence_tables/weights.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netorg629193-my.sharepoint.com/personal/cpien_flowwest_com/Documents/Documents/Github/shasta-sdm/winterRunDSM/wr_sdm/consequence_tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{34636CE1-49ED-4D4D-9578-10AA6B216942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A104E16-4D77-46C0-B26B-97682FE3B294}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{34636CE1-49ED-4D4D-9578-10AA6B216942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2676C90D-9C9F-46CB-ADDE-52486684D771}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9707D464-3622-4F04-9E64-EC8602A7C0C6}"/>
+    <workbookView minimized="1" xWindow="675" yWindow="3330" windowWidth="21600" windowHeight="11235" activeTab="1" xr2:uid="{9707D464-3622-4F04-9E64-EC8602A7C0C6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -135,7 +136,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,6 +149,13 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="97">
@@ -1016,7 +1024,7 @@
     <xf numFmtId="0" fontId="1" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="96" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="61" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1358,61 +1366,61 @@
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="147" t="s">
+      <c r="B1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="147" t="s">
+      <c r="C1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="147" t="s">
+      <c r="D1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="147" t="s">
+      <c r="E1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="147" t="s">
+      <c r="F1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="147" t="s">
+      <c r="G1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="147" t="s">
+      <c r="H1" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="147" t="s">
+      <c r="I1" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="147" t="s">
+      <c r="J1" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="147" t="s">
+      <c r="K1" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="147" t="s">
+      <c r="L1" t="s">
         <v>28</v>
       </c>
-      <c r="M1" s="147" t="s">
+      <c r="M1" t="s">
         <v>29</v>
       </c>
-      <c r="N1" s="147" t="s">
+      <c r="N1" t="s">
         <v>30</v>
       </c>
-      <c r="O1" s="147" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="147" t="s">
+      <c r="P1" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="147" t="s">
+      <c r="Q1" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="147" t="s">
+      <c r="R1" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="147" t="s">
+      <c r="S1" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="147" t="s">
+      <c r="T1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2096,6 +2104,176 @@
       </c>
       <c r="T12" s="146">
         <v>0.15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DC4B137-D446-448C-B253-619E16AE27BA}">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="147">
+        <v>0.33220883499999998</v>
+      </c>
+      <c r="B1" s="147">
+        <v>0.57789473700000005</v>
+      </c>
+      <c r="C1" s="147">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D1" s="147">
+        <v>0.1</v>
+      </c>
+      <c r="E1" s="147">
+        <v>0.181300252</v>
+      </c>
+      <c r="F1" s="147">
+        <v>0.79064725700000005</v>
+      </c>
+      <c r="G1" s="147">
+        <v>0.35957446799999998</v>
+      </c>
+      <c r="H1" s="147">
+        <v>0.57789473700000005</v>
+      </c>
+      <c r="I1" s="147">
+        <v>0.14285714299999999</v>
+      </c>
+      <c r="J1" s="147">
+        <v>8.1059999999999993E-2</v>
+      </c>
+      <c r="K1" s="147">
+        <v>0.36</v>
+      </c>
+      <c r="L1" s="147">
+        <v>0.5</v>
+      </c>
+      <c r="M1" s="147">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0.11</v>
+      </c>
+      <c r="B2">
+        <v>0.09</v>
+      </c>
+      <c r="C2">
+        <v>0.03</v>
+      </c>
+      <c r="D2">
+        <v>0.03</v>
+      </c>
+      <c r="E2">
+        <v>0.01</v>
+      </c>
+      <c r="F2">
+        <v>0.05</v>
+      </c>
+      <c r="G2">
+        <v>0.04</v>
+      </c>
+      <c r="H2">
+        <v>0.06</v>
+      </c>
+      <c r="I2">
+        <v>0.02</v>
+      </c>
+      <c r="J2">
+        <v>0.08</v>
+      </c>
+      <c r="K2">
+        <v>0.04</v>
+      </c>
+      <c r="L2">
+        <v>0.01</v>
+      </c>
+      <c r="M2">
+        <v>0.1</v>
+      </c>
+      <c r="N2">
+        <v>0.1</v>
+      </c>
+      <c r="O2">
+        <v>0.02</v>
+      </c>
+      <c r="P2">
+        <v>0.02</v>
+      </c>
+      <c r="Q2">
+        <v>0.02</v>
+      </c>
+      <c r="R2">
+        <v>0.17</v>
+      </c>
+      <c r="S2">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <f>A1*A2</f>
+        <v>3.6542971850000001E-2</v>
+      </c>
+      <c r="B4">
+        <f t="shared" ref="B4:M4" si="0">B1*B2</f>
+        <v>5.2010526330000001E-2</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>1.8130025200000001E-3</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>3.9532362850000002E-2</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>1.438297872E-2</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>3.4673684220000001E-2</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>2.85714286E-3</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>6.4847999999999998E-3</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>1.44E-2</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="0"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <f>SUM(A4:D4)</f>
+        <v>0.10805349818</v>
       </c>
     </row>
   </sheetData>

--- a/wr_sdm/consequence_tables/weights.xlsx
+++ b/wr_sdm/consequence_tables/weights.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netorg629193-my.sharepoint.com/personal/cpien_flowwest_com/Documents/Documents/Github/shasta-sdm/winterRunDSM/wr_sdm/consequence_tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{34636CE1-49ED-4D4D-9578-10AA6B216942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2676C90D-9C9F-46CB-ADDE-52486684D771}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{34636CE1-49ED-4D4D-9578-10AA6B216942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D38C651-1EA5-4E61-B40A-E25987B57AF3}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="675" yWindow="3330" windowWidth="21600" windowHeight="11235" activeTab="1" xr2:uid="{9707D464-3622-4F04-9E64-EC8602A7C0C6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9707D464-3622-4F04-9E64-EC8602A7C0C6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -123,13 +123,13 @@
     <t>mean_spawners_trib</t>
   </si>
   <si>
-    <t>mean_juv_rear_trib</t>
-  </si>
-  <si>
-    <t>num_trib</t>
-  </si>
-  <si>
     <t>ind_pop</t>
+  </si>
+  <si>
+    <t>mean_rear_prop</t>
+  </si>
+  <si>
+    <t>hab_access</t>
   </si>
 </sst>
 </file>
@@ -1397,13 +1397,13 @@
         <v>27</v>
       </c>
       <c r="L1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" t="s">
         <v>28</v>
-      </c>
-      <c r="M1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N1" t="s">
-        <v>30</v>
       </c>
       <c r="O1" t="s">
         <v>11</v>

--- a/wr_sdm/consequence_tables/weights.xlsx
+++ b/wr_sdm/consequence_tables/weights.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netorg629193-my.sharepoint.com/personal/cpien_flowwest_com/Documents/Documents/Github/shasta-sdm/winterRunDSM/wr_sdm/consequence_tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{34636CE1-49ED-4D4D-9578-10AA6B216942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D38C651-1EA5-4E61-B40A-E25987B57AF3}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{34636CE1-49ED-4D4D-9578-10AA6B216942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F1AB428-A4FD-4AE9-93E3-D0706EAC0B66}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9707D464-3622-4F04-9E64-EC8602A7C0C6}"/>
+    <workbookView xWindow="-24360" yWindow="-270" windowWidth="21600" windowHeight="11235" xr2:uid="{9707D464-3622-4F04-9E64-EC8602A7C0C6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1361,6 +1361,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A7CCEDC-F907-4EAF-BD51-4A41FE57A810}">
   <dimension ref="A1:T12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="9" max="9" width="27.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -1388,10 +1391,10 @@
         <v>24</v>
       </c>
       <c r="I1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" t="s">
         <v>25</v>
-      </c>
-      <c r="J1" t="s">
-        <v>26</v>
       </c>
       <c r="K1" t="s">
         <v>27</v>
